--- a/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
@@ -9454,7 +9454,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2,162.300%</t>
+          <t>2162.300%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2,663.400%</t>
+          <t>2663.400%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2,022.700%</t>
+          <t>2022.700%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2,090.700%</t>
+          <t>2090.700%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1,720.200%</t>
+          <t>1720.200%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1,976.100%</t>
+          <t>1976.100%</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U101"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +617,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -712,6 +713,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -802,6 +804,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -897,6 +900,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -992,6 +996,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1087,6 +1092,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1177,6 +1183,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1272,6 +1279,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1367,6 +1375,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1462,6 +1471,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1557,6 +1567,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1652,6 +1663,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1747,6 +1759,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1842,6 +1855,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1937,6 +1951,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2032,6 +2047,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2127,6 +2143,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2222,6 +2239,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2317,6 +2335,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2412,6 +2431,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2507,6 +2527,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2602,6 +2623,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2611,7 +2633,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2626,7 +2648,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2636,12 +2658,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-151178</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2669,7 +2691,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALSE-134719540</t>
+          <t>ALSE-134713536</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2679,7 +2701,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134719540/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134713536/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2697,6 +2719,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2706,12 +2729,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01/26/2026</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2721,35 +2744,35 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>38.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>32.900%</t>
+          <t>-1.200%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>174721</t>
+          <t>-151178</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1604</v>
+        <v>5787</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>531068</t>
+          <t>12598171</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>84.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2764,7 +2787,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALSE-134745491</t>
+          <t>ALSE-134719540</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2774,7 +2797,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134745491/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134719540/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2792,6 +2815,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2816,35 +2840,35 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7.100%</t>
+          <t>38.000%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7.100%</t>
+          <t>32.900%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66188</t>
+          <t>174721</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3048</v>
+        <v>1604</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>932224</t>
+          <t>531068</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13.100%</t>
+          <t>84.900%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2859,7 +2883,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALSE-134745748</t>
+          <t>ALSE-134745491</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2869,7 +2893,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134745748/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134745491/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2887,6 +2911,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2896,55 +2921,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>01/26/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>12.100%</t>
+          <t>7.100%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12.100%</t>
+          <t>7.100%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>217353</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2411</v>
+        <v>3048</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1796401</t>
+          <t>932224</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>13.100%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2954,7 +2979,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALSE-134765369</t>
+          <t>ALSE-134745748</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2964,7 +2989,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134765369/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134745748/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2982,6 +3007,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2991,12 +3017,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3006,60 +3032,60 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.100%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>12.100%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-81404</t>
+          <t>217353</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>947</v>
+        <v>2411</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1628089</t>
+          <t>1796401</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALSE-134881194</t>
+          <t>ALSE-134765369</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134881194/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134765369/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3077,6 +3103,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3086,12 +3113,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07/06/2024</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COUNTRY Preferred Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3101,60 +3128,60 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13.621%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.255%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>889927</t>
+          <t>-81404</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>14752</v>
+        <v>947</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16933504</t>
+          <t>1628089</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>224.300%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-78.700%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>CFPC-133804773</t>
+          <t>ALSE-134881194</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133804773/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134881194/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3164,14 +3191,15 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3181,12 +3209,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05/29/2024</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COUNTRY Mutual Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3196,60 +3224,55 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.932%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.472%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>80069</t>
+          <t>-740711</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1496</v>
+        <v>8816</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3239050</t>
+          <t>18517786</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5.700%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-40.000%</t>
+          <t>-4.100%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>CFPC-133945376</t>
+          <t>ALSE-134905779</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134905779/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3259,14 +3282,15 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3276,12 +3300,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05/29/2024</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>COUNTRY Preferred Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3291,40 +3315,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.932%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.549%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>173673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3573</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6813382</t>
+          <t>46763973</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-40.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3334,7 +3358,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CFPC-133945376</t>
+          <t>ALSE-134914477</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3344,7 +3368,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134914477/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3354,14 +3378,15 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3371,55 +3396,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>05/29/2024</t>
+          <t>07/06/2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COUNTRY Casualty Insurance Company</t>
+          <t>COUNTRY Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.932%</t>
+          <t>13.621%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.069%</t>
+          <t>5.255%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>889927</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>48</v>
+        <v>14752</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>123337</t>
+          <t>16933504</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5.200%</t>
+          <t>224.300%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-40.000%</t>
+          <t>-78.700%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3429,17 +3454,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CFPC-133945376</t>
+          <t>CFPC-133804773</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133804773/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3457,6 +3482,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3466,55 +3492,55 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07/06/2025</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>COUNTRY Preferred Insurance Company</t>
+          <t>COUNTRY Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18.687%</t>
+          <t>2.932%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.484%</t>
+          <t>2.472%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2205460</t>
+          <t>80069</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>13794</v>
+        <v>1496</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19204296</t>
+          <t>3239050</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>45.000%</t>
+          <t>5.700%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-12.500%</t>
+          <t>-40.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3524,7 +3550,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CFPC-134388842</t>
+          <t>CFPC-133945376</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3534,7 +3560,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134388842/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3544,14 +3570,15 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3561,7 +3588,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3571,45 +3598,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.932%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.549%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173673</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3573</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6813382</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-40.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3619,7 +3646,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CFPC-134624320</t>
+          <t>CFPC-133945376</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3629,7 +3656,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134624320/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3639,14 +3666,15 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3656,12 +3684,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>COUNTRY Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3671,40 +3699,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.932%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.069%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>26243</v>
+        <v>48</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10391611</t>
+          <t>123337</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67.900%</t>
+          <t>5.200%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-23.300%</t>
+          <t>-40.000%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3714,7 +3742,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-133945376</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3724,7 +3752,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133945376/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3742,6 +3770,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3751,12 +3780,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>COUNTRY Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3766,40 +3795,40 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>30.976%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.014%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448258</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>15441</v>
+        <v>1307</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4853420</t>
+          <t>3177823</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>65.600%</t>
+          <t>2090.700%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-17.300%</t>
+          <t>-14.400%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3809,17 +3838,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-133947234</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3837,6 +3866,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3846,12 +3876,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>COUNTRY Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3861,40 +3891,40 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>30.976%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.105%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658276</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2758</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5418322</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1720.200%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-19.500%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3904,17 +3934,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-133947234</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3932,6 +3962,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3941,12 +3972,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>05/29/2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>COUNTRY Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3956,40 +3987,40 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>30.976%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>23.733%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321170</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>54469</v>
+        <v>421</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12100804</t>
+          <t>1182172</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>86.800%</t>
+          <t>1976.100%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-28.000%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3999,17 +4030,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-133947234</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4027,6 +4058,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4036,12 +4068,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>07/06/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>COUNTRY Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4051,40 +4083,40 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.948%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.618%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717726</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>25392</v>
+        <v>2833</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5559947</t>
+          <t>7462251</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>83.500%</t>
+          <t>2162.300%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-30.700%</t>
+          <t>-51.000%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4094,7 +4126,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-134283900</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4104,7 +4136,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4114,14 +4146,15 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4131,12 +4164,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>07/06/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>COUNTRY Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4146,40 +4179,40 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.948%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.494%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1351171</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>191287</v>
+        <v>6296</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>45519940</t>
+          <t>14232537</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>142.230%</t>
+          <t>2663.400%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-36.300%</t>
+          <t>-73.500%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4189,7 +4222,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-134283900</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4199,7 +4232,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4209,14 +4242,15 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4226,12 +4260,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>07/06/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>COUNTRY Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4241,40 +4275,40 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.948%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.177%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207738</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>76501</v>
+        <v>515</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>25408263</t>
+          <t>2041232</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>144.000%</t>
+          <t>2022.700%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-22.700%</t>
+          <t>-43.700%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4284,7 +4318,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GECC-133899418</t>
+          <t>CFPC-134283900</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4294,7 +4328,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4304,14 +4338,15 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4321,55 +4356,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>07/06/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>COUNTRY Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>18.687%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.484%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2205460</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>89</v>
+        <v>13794</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>79638</t>
+          <t>19204296</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28.000%</t>
+          <t>45.000%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-16.900%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4379,7 +4414,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>CFPC-134388842</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4389,7 +4424,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134388842/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4407,6 +4442,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4416,22 +4452,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>COUNTRY Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4450,21 +4486,21 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>261645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-24.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4474,7 +4510,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>CFPC-134624320</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4484,7 +4520,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134624320/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4502,6 +4538,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4511,12 +4548,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4526,7 +4563,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4545,21 +4582,21 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>282</v>
+        <v>26243</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>168316</t>
+          <t>10391611</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>67.900%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-22.000%</t>
+          <t>-23.300%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4569,7 +4606,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4579,7 +4616,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4589,14 +4626,15 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4606,12 +4644,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4621,7 +4659,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4640,21 +4678,21 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1462</v>
+        <v>15441</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>844007</t>
+          <t>4853420</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>65.600%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-26.500%</t>
+          <t>-17.300%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4664,7 +4702,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4674,7 +4712,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4684,14 +4722,15 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4701,12 +4740,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4716,7 +4755,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4735,21 +4774,21 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>187254</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-18.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4759,7 +4798,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4769,7 +4808,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4779,14 +4818,15 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4796,12 +4836,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4811,7 +4851,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4830,21 +4870,21 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>191</v>
+        <v>54469</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>12100804</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>86.800%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-16.700%</t>
+          <t>-28.000%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4854,7 +4894,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GECC-134659607</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4864,7 +4904,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4874,14 +4914,15 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4891,12 +4932,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4911,55 +4952,55 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-182387</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3595</v>
+        <v>25392</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3647738</t>
+          <t>5559947</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>83.500%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-9.600%</t>
+          <t>-30.700%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GECC-134904117</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134904117/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4969,14 +5010,15 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4986,12 +5028,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5006,55 +5048,55 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-3481</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>66</v>
+        <v>191287</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>75671</t>
+          <t>45519940</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.200%</t>
+          <t>142.230%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-8.100%</t>
+          <t>-36.300%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GECC-134904117</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134904117/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5064,14 +5106,15 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5081,12 +5124,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/06/2024</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5096,40 +5139,40 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>8.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>91844</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7576</v>
+        <v>76501</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2624111</t>
+          <t>25408263</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>190.500%</t>
+          <t>144.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-57.600%</t>
+          <t>-22.700%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5139,7 +5182,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>PRGS-133865398</t>
+          <t>GECC-133899418</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5149,7 +5192,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133865398/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133899418/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5167,6 +5210,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5176,12 +5220,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/06/2024</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5191,40 +5235,40 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>8.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-40190</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2270</v>
+        <v>89</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>855104</t>
+          <t>79638</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>135.700%</t>
+          <t>28.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-47.100%</t>
+          <t>-16.900%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5234,7 +5278,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>PRGS-133865398</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5244,7 +5288,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133865398/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5254,14 +5298,15 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5271,12 +5316,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03/15/2024</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5286,60 +5331,60 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>15</v>
+        <v>509</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>261645</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>28.900%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-24.300%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>PRGS-133991830</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5349,14 +5394,15 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5366,12 +5412,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/15/2024</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5381,60 +5427,60 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>342651</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>21451</v>
+        <v>282</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23107567</t>
+          <t>168316</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4.700%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-1.200%</t>
+          <t>-22.000%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>PRGS-133991830</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5444,14 +5490,15 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5461,12 +5508,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>03/15/2024</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5476,60 +5523,60 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>208</v>
+        <v>1462</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>260123</t>
+          <t>844007</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-26.500%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>PRGS-133991830</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5539,14 +5586,15 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5556,12 +5604,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>03/15/2024</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5571,60 +5619,60 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>66557</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>10681</v>
+        <v>166</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>10848770</t>
+          <t>187254</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-18.000%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PRGS-133991830</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5634,14 +5682,15 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5651,12 +5700,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02/28/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5671,35 +5720,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6135</v>
+        <v>191</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3407246</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>88.000%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-42.500%</t>
+          <t>-16.700%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5709,7 +5758,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PRGS-134231435</t>
+          <t>GECC-134659607</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5719,7 +5768,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134231435/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134659607/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5737,6 +5786,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5746,12 +5796,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02/28/2025</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5761,60 +5811,60 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>-1.100%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-25022</t>
+          <t>-182387</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1647</v>
+        <v>3595</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1087926</t>
+          <t>3647738</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>58.600%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-33.300%</t>
+          <t>-9.600%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>PRGS-134231435</t>
+          <t>GECC-134904117</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134231435/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134904117/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5832,6 +5882,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5841,12 +5892,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5861,35 +5912,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-5.863%</t>
+          <t>-1.100%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-2.990%</t>
+          <t>-4.600%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-247</t>
+          <t>-3481</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>75671</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>14.800%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-4.600%</t>
+          <t>-8.100%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5899,7 +5950,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PRGS-134901848</t>
+          <t>GECC-134904117</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5909,7 +5960,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134904117/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5927,6 +5978,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5936,7 +5988,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>12/06/2024</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5951,60 +6003,60 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-3.270%</t>
+          <t>8.400%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.310%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-1097616</t>
+          <t>91844</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>31099</v>
+        <v>7576</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>33201839</t>
+          <t>2624111</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>20.900%</t>
+          <t>190.500%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-8.800%</t>
+          <t>-57.600%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PRGS-134901848</t>
+          <t>PRGS-133865398</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133865398/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6014,14 +6066,15 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6031,7 +6084,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>12/06/2024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6046,60 +6099,60 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-5.863%</t>
+          <t>8.400%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-2.990%</t>
+          <t>-4.700%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-5279</t>
+          <t>-40190</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>159</v>
+        <v>2270</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>176617</t>
+          <t>855104</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>14.800%</t>
+          <t>135.700%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-4.600%</t>
+          <t>-47.100%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-134901848</t>
+          <t>PRGS-133865398</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133865398/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6109,14 +6162,15 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6126,12 +6180,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>03/15/2024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6146,35 +6200,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-5.863%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-2.990%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-365407</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11887</v>
+        <v>15</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>12226080</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>14.800%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-4.600%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6184,7 +6238,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134901848</t>
+          <t>PRGS-133991830</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6194,7 +6248,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6204,14 +6258,15 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6221,75 +6276,75 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>02/17/2024</t>
+          <t>03/15/2024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Indiana</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3807234</t>
+          <t>342651</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>12318</v>
+        <v>21451</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19078797</t>
+          <t>23107567</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>4.700%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-1.200%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>LBPM-133920436</t>
+          <t>PRGS-133991830</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133920436/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6307,6 +6362,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6316,75 +6372,75 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>02/17/2024</t>
+          <t>03/15/2024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15.100%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>859</v>
+        <v>208</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>567244</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>23.500%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>LBPM-133920436</t>
+          <t>PRGS-133991830</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133920436/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6402,6 +6458,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6411,12 +6468,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>04/20/2024</t>
+          <t>03/15/2024</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Indiana</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6426,60 +6483,60 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1927132</t>
+          <t>66557</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9336</v>
+        <v>10681</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19259915</t>
+          <t>10848770</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>19.600%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>LBPM-133945073</t>
+          <t>PRGS-133991830</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133945073/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133991830/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6497,6 +6554,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6506,12 +6564,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09/01/2024</t>
+          <t>02/28/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Indiana</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6526,35 +6584,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>-2.100%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17.000%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>76443</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>549</v>
+        <v>6135</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>449010</t>
+          <t>3407246</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>88.000%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-42.500%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6564,7 +6622,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>LBPM-134109613</t>
+          <t>PRGS-134231435</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6574,7 +6632,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134109613/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134231435/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6584,14 +6642,15 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6601,12 +6660,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>02/28/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6616,40 +6675,40 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14.100%</t>
+          <t>-2.100%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14.100%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>83047</t>
+          <t>-25022</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1556</v>
+        <v>1647</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>590523</t>
+          <t>1087926</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>27.400%</t>
+          <t>58.600%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-33.300%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6659,7 +6718,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>LBPM-134153594</t>
+          <t>PRGS-134231435</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6669,7 +6728,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134153594/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134231435/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6679,14 +6738,15 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6696,12 +6756,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/14/2024</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Indiana</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6711,60 +6771,60 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>-5.863%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-2.990%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-606723</t>
+          <t>-247</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9003</v>
+        <v>11</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>20528412</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.800%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>-4.600%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>LBPM-134313457</t>
+          <t>PRGS-134901848</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134313457/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6774,14 +6834,15 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6791,12 +6852,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6806,60 +6867,60 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>-3.270%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>-3.310%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>55469</t>
+          <t>-1097616</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1383</v>
+        <v>31099</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>585407</t>
+          <t>33201839</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>23.200%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.800%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>LBPM-134579873</t>
+          <t>PRGS-134901848</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134579873/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6877,6 +6938,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6886,12 +6948,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6906,55 +6968,55 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.863%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.990%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5279</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9299</v>
+        <v>159</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>13928197</t>
+          <t>176617</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>23.500%</t>
+          <t>14.800%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-24.000%</t>
+          <t>-4.600%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>SFMA-133814624</t>
+          <t>PRGS-134901848</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133814624/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6964,14 +7026,15 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6981,12 +7044,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7001,55 +7064,55 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.863%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.990%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-365407</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>175210</v>
+        <v>11887</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>138828560</t>
+          <t>12226080</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20.800%</t>
+          <t>14.800%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-20.600%</t>
+          <t>-4.600%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>SFMA-133814624</t>
+          <t>PRGS-134901848</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133814624/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134901848/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7059,14 +7122,15 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7076,12 +7140,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>07/15/2024</t>
+          <t>02/17/2024</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Indiana</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7096,35 +7160,35 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5181471</t>
+          <t>3807234</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>77479</v>
+        <v>12318</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>59233249</t>
+          <t>19078797</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>22.100%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7134,7 +7198,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>SFMA-134021088</t>
+          <t>LBPM-133920436</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7144,7 +7208,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134021088/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133920436/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7162,6 +7226,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7171,55 +7236,55 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>02/17/2024</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.100%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>371</v>
+        <v>859</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>174411</t>
+          <t>567244</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>23.500%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7229,7 +7294,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>SFMA-134076028</t>
+          <t>LBPM-133920436</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7239,7 +7304,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134076028/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133920436/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7257,6 +7322,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7266,12 +7332,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>04/20/2024</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Indiana</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7281,40 +7347,40 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1927132</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6142</v>
+        <v>9336</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1504944</t>
+          <t>19259915</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>19.600%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-9.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7324,7 +7390,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>SFMA-134076028</t>
+          <t>LBPM-133945073</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7334,7 +7400,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134076028/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133945073/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7352,6 +7418,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7361,12 +7428,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>09/01/2024</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Indiana</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7376,40 +7443,40 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76443</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8768</v>
+        <v>549</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>14820478</t>
+          <t>449010</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>22.100%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7419,7 +7486,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>SFMA-134293675</t>
+          <t>LBPM-134109613</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7429,7 +7496,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134293675/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134109613/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7439,14 +7506,15 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7456,12 +7524,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7471,40 +7539,40 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.100%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.100%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83047</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>180691</v>
+        <v>1556</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>159242875</t>
+          <t>590523</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>27.400%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-18.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7514,7 +7582,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>SFMA-134293675</t>
+          <t>LBPM-134153594</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7524,7 +7592,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134293675/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134153594/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7534,14 +7602,15 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7551,12 +7620,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>04/21/2025</t>
+          <t>12/14/2024</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Indiana</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7571,35 +7640,35 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>14.900%</t>
+          <t>-6.000%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>401094</t>
+          <t>-606723</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10159</v>
+        <v>9003</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>16131053</t>
+          <t>20528412</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>140.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-11.400%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7609,7 +7678,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134388424</t>
+          <t>LBPM-134313457</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7619,7 +7688,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134388424/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134313457/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7629,14 +7698,15 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7646,12 +7716,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>04/21/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7661,40 +7731,40 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-457061</t>
+          <t>55469</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>222612</v>
+        <v>1383</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>191923955</t>
+          <t>585407</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>166.700%</t>
+          <t>23.200%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7704,7 +7774,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-134388424</t>
+          <t>LBPM-134579873</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7714,7 +7784,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134388424/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134579873/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7732,6 +7802,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7741,7 +7812,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>07/15/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7751,45 +7822,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>15.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7435657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>79425</v>
+        <v>9299</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>67390405</t>
+          <t>13928197</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18.100%</t>
+          <t>23.500%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.000%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7799,7 +7870,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134464935</t>
+          <t>SFMA-133814624</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7809,7 +7880,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134464935/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133814624/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7819,14 +7890,15 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7836,55 +7908,55 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>23.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1793</v>
+        <v>175210</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>648658</t>
+          <t>138828560</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>27.900%</t>
+          <t>20.800%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-20.600%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7894,7 +7966,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134737639</t>
+          <t>SFMA-133814624</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7904,7 +7976,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134737639/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133814624/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7914,14 +7986,15 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7931,12 +8004,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>08/30/2024</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>United Services Automobile Association</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7946,35 +8019,40 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5181471</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11044</v>
+        <v>77479</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>21453676</t>
+          <t>59233249</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>22.100%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-82.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7984,7 +8062,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>USAA-133861378</t>
+          <t>SFMA-134021088</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7994,7 +8072,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134021088/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8012,6 +8090,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8021,22 +8100,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>08/30/2024</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USAA Casualty Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8050,21 +8134,21 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6969</v>
+        <v>371</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>11998542</t>
+          <t>174411</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-86.000%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8074,7 +8158,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>USAA-133861378</t>
+          <t>SFMA-134076028</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8084,7 +8168,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134076028/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -8102,6 +8186,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8111,22 +8196,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>08/30/2024</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USAA General Indemnity Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8140,21 +8230,21 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4815</v>
+        <v>6142</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>9358626</t>
+          <t>1504944</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-68.800%</t>
+          <t>-9.000%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8164,7 +8254,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>USAA-133861378</t>
+          <t>SFMA-134076028</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8174,7 +8264,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134076028/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8192,6 +8282,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8201,22 +8292,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>08/30/2024</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Garrison Property and Casualty Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8230,21 +8326,21 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2927</v>
+        <v>8768</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>5477573</t>
+          <t>14820478</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>22.100%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-65.500%</t>
+          <t>-18.900%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8254,7 +8350,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>USAA-133861378</t>
+          <t>SFMA-134293675</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8264,7 +8360,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134293675/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8274,14 +8370,15 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8291,55 +8388,55 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>05/30/2024</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>United Services Automobile Association</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>96395</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2816</v>
+        <v>180691</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>950152</t>
+          <t>159242875</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-18.200%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8349,7 +8446,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>USAA-133990216</t>
+          <t>SFMA-134293675</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8359,7 +8456,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134293675/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8369,14 +8466,15 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8386,55 +8484,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>05/30/2024</t>
+          <t>04/21/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USAA Casualty Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>14.900%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>401094</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2637</v>
+        <v>10159</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>724456</t>
+          <t>16131053</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>140.000%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-11.400%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8444,7 +8542,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>USAA-133990216</t>
+          <t>SFMA-134388424</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8454,7 +8552,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134388424/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8464,14 +8562,15 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8481,55 +8580,55 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>05/30/2024</t>
+          <t>04/21/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USAA General Indemnity Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>100329</t>
+          <t>-457061</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4279</v>
+        <v>222612</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1006855</t>
+          <t>191923955</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>166.700%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-15.200%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8539,7 +8638,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>USAA-133990216</t>
+          <t>SFMA-134388424</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8549,7 +8648,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134388424/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8559,14 +8658,15 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8576,12 +8676,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>05/30/2024</t>
+          <t>07/15/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Garrison Property and Casualty Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8591,40 +8691,40 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>15.500%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>7435657</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1804</v>
+        <v>79425</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>446792</t>
+          <t>67390405</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>18.100%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8634,7 +8734,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>USAA-133990216</t>
+          <t>SFMA-134464935</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8644,7 +8744,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134464935/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8654,14 +8754,15 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8671,12 +8772,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>04/27/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>United Services Automobile Association</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8686,35 +8787,40 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>12.900%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-921513</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>10049</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>34741188</t>
+          <t>16154975</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>204.300%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-26.200%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8724,7 +8830,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>USAA-134333877</t>
+          <t>SFMA-134610192</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8734,7 +8840,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134610192/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8752,6 +8858,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8761,12 +8868,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>04/27/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USAA Casualty Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8776,35 +8883,40 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.600%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14429498</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>233049</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>28627584</t>
+          <t>190380437</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>513.400%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-66.900%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8814,7 +8926,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>USAA-134333877</t>
+          <t>SFMA-134610192</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8824,7 +8936,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134610192/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8842,6 +8954,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8851,45 +8964,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USAA General Indemnity Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>23.500%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>19.300%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125506</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1793</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>26668896</t>
+          <t>648658</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.900%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8904,7 +9022,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>USAA-134333877</t>
+          <t>SFMA-134737639</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8914,7 +9032,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134737639/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8932,6 +9050,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8941,22 +9060,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>08/30/2024</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Garrison Property and Casualty Insurance Company</t>
+          <t>United Services Automobile Association</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8970,21 +9089,21 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>11044</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>14194876</t>
+          <t>21453676</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-82.500%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8994,7 +9113,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>USAA-134333877</t>
+          <t>USAA-133861378</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9004,7 +9123,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -9014,14 +9133,15 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9031,12 +9151,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>06/14/2025</t>
+          <t>08/30/2024</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>United Services Automobile Association</t>
+          <t>USAA Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9049,37 +9169,32 @@
           <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>13.900%</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2277630</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>11218</v>
+        <v>6969</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>18564778</t>
+          <t>11998542</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>-86.000%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9089,7 +9204,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>USAA-134423223</t>
+          <t>USAA-133861378</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9099,7 +9214,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -9109,14 +9224,15 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9126,12 +9242,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>06/14/2025</t>
+          <t>08/30/2024</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USAA Casualty Insurance Company</t>
+          <t>USAA General Indemnity Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9144,37 +9260,32 @@
           <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>10.800%</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>545941</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7150</v>
+        <v>4815</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>10052644</t>
+          <t>9358626</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>-68.800%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9184,7 +9295,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>USAA-134423223</t>
+          <t>USAA-133861378</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9194,7 +9305,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9204,14 +9315,15 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9221,12 +9333,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>06/14/2025</t>
+          <t>08/30/2024</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USAA General Indemnity Company</t>
+          <t>Garrison Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9239,37 +9351,32 @@
           <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>13.800%</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>762657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4858</v>
+        <v>2927</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8324598</t>
+          <t>5477573</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>10.100%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>6.600%</t>
+          <t>-65.500%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9279,7 +9386,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>USAA-134423223</t>
+          <t>USAA-133861378</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9289,7 +9396,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133861378/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -9299,14 +9406,15 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9316,12 +9424,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>06/14/2025</t>
+          <t>05/30/2024</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Garrison Property and Casualty Insurance Company</t>
+          <t>United Services Automobile Association</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9331,40 +9439,40 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>7.700%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>259723</t>
+          <t>96395</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3176</v>
+        <v>2816</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4778778</t>
+          <t>950152</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>9.300%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9374,7 +9482,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>USAA-134423223</t>
+          <t>USAA-133990216</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9384,7 +9492,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9394,14 +9502,15 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9411,55 +9520,55 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>07/06/2025</t>
+          <t>05/30/2024</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>COUNTRY Mutual Insurance Company</t>
+          <t>USAA Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>13.948%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9.618%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>717726</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2833</v>
+        <v>2637</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>7462251</t>
+          <t>724456</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2162.300%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-51.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9469,7 +9578,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>CFPC-134283900</t>
+          <t>USAA-133990216</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -9479,7 +9588,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9489,14 +9598,15 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9506,55 +9616,55 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>07/06/2025</t>
+          <t>05/30/2024</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>COUNTRY Preferred Insurance Company</t>
+          <t>USAA General Indemnity Company</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>13.948%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>9.494%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1351171</t>
+          <t>100329</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6296</v>
+        <v>4279</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>14232537</t>
+          <t>1006855</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2663.400%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-73.500%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9564,7 +9674,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>CFPC-134283900</t>
+          <t>USAA-133990216</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9574,7 +9684,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9584,14 +9694,15 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9601,55 +9712,55 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>07/06/2025</t>
+          <t>05/30/2024</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>COUNTRY Casualty Insurance Company</t>
+          <t>Garrison Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>13.948%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>10.177%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>207738</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>515</v>
+        <v>1804</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2041232</t>
+          <t>446792</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2022.700%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-43.700%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9659,7 +9770,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>CFPC-134283900</t>
+          <t>USAA-133990216</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9669,7 +9780,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/134283900/filing_summary.pdf</t>
+          <t>output/pdfs/AK/133990216/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9679,14 +9790,15 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9696,12 +9808,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>08/28/2024</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>COUNTRY Mutual Insurance Company</t>
+          <t>United Services Automobile Association</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -9711,40 +9823,35 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>30.976%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>11.014%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>448258</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1307</v>
+        <v>0</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>3177823</t>
+          <t>34741188</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2090.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-14.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9754,17 +9861,17 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>CFPC-133947234</t>
+          <t>USAA-134333877</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9774,14 +9881,15 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9791,12 +9899,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>08/28/2024</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>COUNTRY Preferred Insurance Company</t>
+          <t>USAA Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -9806,40 +9914,35 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>30.976%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>9.105%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>658276</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2758</v>
+        <v>0</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>5418322</t>
+          <t>28627584</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1720.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-19.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9849,17 +9952,17 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>CFPC-133947234</t>
+          <t>USAA-134333877</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9869,14 +9972,15 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9886,12 +9990,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>08/28/2024</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>COUNTRY Casualty Insurance Company</t>
+          <t>USAA General Indemnity Company</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9901,40 +10005,35 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>30.976%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23.733%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>321170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1182172</t>
+          <t>26668896</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1976.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9944,17 +10043,17 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>CFPC-133947234</t>
+          <t>USAA-134333877</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>output/pdfs/AK/133947234/filing_summary.pdf</t>
+          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9964,14 +10063,490 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10/18/2025</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>14194876</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>USAA-134333877</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134333877/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>06/14/2025</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>13.900%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2277630</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>11218</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>18564778</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>6.700%</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>USAA-134423223</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>06/14/2025</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10.800%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5.400%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>545941</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>7150</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>10052644</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>9.100%</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>USAA-134423223</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>06/14/2025</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>13.800%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>9.200%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>762657</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>4858</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>8324598</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>10.100%</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>6.600%</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>USAA-134423223</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>06/14/2025</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>5.400%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>259723</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>3176</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>4778778</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>9.300%</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>USAA-134423223</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134423223/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ak_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U106"/>
+  <dimension ref="A1:U107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10547,6 +10547,102 @@
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>6.100%</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1.800%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1348683</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>79722</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76586173</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>23.200%</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-5.400%</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>SFMA-134887915</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>output/pdfs/AK/134887915/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
